--- a/output/laminas_comunales/comunal_s_isapre_a_2023_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_tarapaca.xlsx
@@ -384,22 +384,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>32174</v>
+        <v>14.94567363301482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C3">
-        <v>7020</v>
+        <v>7.198838896952105</v>
       </c>
     </row>
     <row r="4">
@@ -414,52 +414,52 @@
         </is>
       </c>
       <c r="C4">
-        <v>1021</v>
+        <v>5.537176636477033</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C5">
-        <v>496</v>
+        <v>5.208062852861096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Colchane</t>
         </is>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>3.414264036418817</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C7">
-        <v>45</v>
+        <v>1.627074520013017</v>
       </c>
     </row>
     <row r="8">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>1.484375</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_isapre_a_2023_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,106 +375,3571 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C2">
-        <v>14.94567363301482</v>
+        <v>95.46875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C3">
-        <v>7.198838896952105</v>
+        <v>93.78457533355028</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C4">
-        <v>5.537176636477033</v>
+        <v>89.97559184218531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Colchane</t>
         </is>
       </c>
       <c r="C5">
-        <v>5.208062852861096</v>
+        <v>88.84673748103187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C6">
-        <v>3.414264036418817</v>
+        <v>88.388969521045</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="C7">
-        <v>1.627074520013017</v>
+        <v>86.5285536091979</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>77.28419262982352</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>1402</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Camiña</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="C9">
+        <v>48.671875</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>48.55842185128984</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>48.45427920598763</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>46.796875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>45.46520168260492</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>45.33029612756264</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>45.31204644412192</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>45.11632951895439</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>44.51039015958039</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>43.07692307692308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>42.8125</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>41.41222409024351</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>40.28831562974203</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>40.07562490419142</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>37.4051593323217</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>37.20856772563211</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>37.09729905629678</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>30.546875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>30.00325414904002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>29.95777454673833</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>29.3033381712627</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>28.45220030349014</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>27.44619447885987</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>27.41651890704869</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>25.68469005911383</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>24.99186462739993</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>24.25253991291727</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>23.85161885134769</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>23.39606269320462</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>23.125</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>22.02001617318664</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>21.37902382206527</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>21.25022645663878</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>20.2322206095791</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>20.11611030478955</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>19.54552849937632</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>19.34749620637329</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>17.1875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>16.76783004552352</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>16.59616010413277</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>15.85735963581184</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>15.72582739203656</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>14.94567363301482</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>14.80637813211845</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>14.71698113207547</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>14.60483266686945</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>14.01919843809317</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>13.89119861756932</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>13.83127470699995</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>13.73385463421148</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>13.73292867981791</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>13.70585256859894</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>13.671875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>13.59941944847605</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>13.59618200553175</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>13.52685050798258</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>13.24865903509878</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>13.12594840667678</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>12.95151317930361</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>12.734375</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>12.59829708769456</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>12.43017517218938</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>12.1849930088771</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>12.17988321805336</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>12.04035144809632</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>11.64005805515239</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>11.53262518968133</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>11.484375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>11.29189716889034</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>10.74589010233517</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>10.68214804063861</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>10.546875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>10.3125</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>10.31226120438308</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>10.0878620240807</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>9.995119041162752</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>9.582949183795217</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>9.492017416545718</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>9.375</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>9.327690885526749</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>9.300283825653937</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>9.216255442670537</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>9.140625</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>8.981451350471852</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>8.72111942726977</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>8.510124353727592</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>8.35728618688649</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>8.193317322655419</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>8.131848565557048</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>7.587253414264036</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>7.198838896952105</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>7.132018209408194</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>6.752655538694992</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>6.435549279287231</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>5.93214680505375</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>5.537176636477033</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>5.208062852861096</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>4.513788098693759</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>4.44180180514974</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>3.828841043440534</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>3.575164513951228</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>3.414264036418817</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>3.175502733738091</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>2.988298579013625</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>2.890748026923952</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>2.685050798258346</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>2.588805841884491</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>2.469422547184273</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>2.370942942217556</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>2.352048558421851</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>2.233443116414971</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>1.895267869170774</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>1.785195936139332</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>1.759761408402638</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>1.75823256980671</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>1.712626995645864</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>1.708335593036499</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>1.662075597032605</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>1.632898338909868</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>1.627074520013017</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>1.496827376755789</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>1.494920174165457</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C131">
         <v>1.484375</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>1.263626010087315</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>1.263437469860747</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>1.23367198838897</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>1.198893101171443</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>1.193123271327079</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>1.182276696133196</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>1.138088012139606</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>1.132075471698113</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>1.132075471698113</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>1.087609706879539</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>1.073869183208591</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>1.062215477996965</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>1.062215477996965</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>1.058191226953682</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>1.044992743105951</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>1.015625</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>0.9724238026124818</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>0.9637141945678865</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>0.9544986170616628</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>0.9288824383164006</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>0.9165356038830739</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>0.9104704097116844</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>0.8998548621190131</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>0.8783969256107603</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.8731493031075438</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>0.8502051323901447</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>0.7982583454281568</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>0.7592602635717772</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0.7582108597755043</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0.6616410868268344</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>0.6616410868268344</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>0.6182547860513044</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>0.6069802731411229</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0.6069802731411229</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0.6069802731411229</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>0.6038978863573977</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0.5805515239477503</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0.5660377358490566</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0.5532053368044256</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>0.546875</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>0.5311077389984825</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>0.4889050455890972</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>0.4087810016989265</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>0.390625</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>0.390497884803124</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>0.390497884803124</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>0.3793626707132018</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>0.3793626707132018</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>0.3254149040026033</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>0.3199739682195347</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>0.3125</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>0.3034901365705615</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>0.292873413602343</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>0.2603319232020826</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>0.2603319232020826</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>0.234375</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>0.2277904328018223</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>0.2277904328018223</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>0.2277904328018223</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0.195248942401562</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>0.195248942401562</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>0.1627074520013017</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>0.160726147728698</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>0.1517450682852807</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>0.1247356147296491</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>0.1045184486675059</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>0.09762447120078099</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>0.09644560838631659</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>0.08708272859216255</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>0.08129212674139348</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>0.078125</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>0.078125</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>0.07587253414264036</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>0.07587253414264036</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>0.03561068617340921</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>0.02902757619738752</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>0.02169315038776506</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>0.02169315038776506</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>0.01483778590558717</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>0.006038843700789231</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>0.006038843700789231</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>0.005423287596941266</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>0.004451335771676151</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>0.002967557181117434</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
